--- a/programs/defi-program/worksheets/On-Chain-Operator-Worksheets.xlsx
+++ b/programs/defi-program/worksheets/On-Chain-Operator-Worksheets.xlsx
@@ -28,7 +28,7 @@
     <sheet name="W17 Letter" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Start'!$A$5:$C$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Start'!$A$5:$D$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Start'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tools'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'W1 Records'!$A$4:$I$44</definedName>
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'W14 Alerts'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'W15 Automation'!$A$4:$F$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="16">'W15 Automation'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'W16 Annual review'!$A$13:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'W16 Annual review'!$A$14:$D$20</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,11 +66,11 @@
     <numFmt numFmtId="168" formatCode="0.0&quot;×&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0&quot;%&quot;"/>
-    <numFmt numFmtId="171" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="172" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="173" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,6 +134,18 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="003E4C59"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="8">
@@ -244,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -288,6 +300,12 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -314,6 +332,9 @@
     <xf numFmtId="2" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -335,9 +356,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -367,12 +385,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="172" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -386,6 +404,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -413,6 +434,9 @@
     <xf numFmtId="172" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,7 +548,7 @@
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
-        <t>The LTV at which liquidation can start. 0.80 means 80%.</t>
+        <t>Use 0 to 1. 0.80 means 80%.</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0" shapeId="0">
@@ -532,322 +556,322 @@
         <t>Amount borrowed.</t>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
+    <comment ref="B15" authorId="0" shapeId="0">
       <text>
-        <t>Loan-to-value used on each loop.</t>
+        <t>Use 0 to 1. Loan-to-value on each loop.</t>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
+    <comment ref="B16" authorId="0" shapeId="0">
       <text>
         <t>How many times you borrow and deposit again.</t>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0">
+    <comment ref="B17" authorId="0" shapeId="0">
       <text>
         <t>Yield on the collateral, in percentage points.</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0">
+    <comment ref="B18" authorId="0" shapeId="0">
       <text>
         <t>Cost of the debt, in percentage points.</t>
       </text>
     </comment>
-    <comment ref="B20" authorId="0" shapeId="0">
+    <comment ref="B21" authorId="0" shapeId="0">
       <text>
         <t>2 means the price doubled. 0.5 means it halved.</t>
       </text>
     </comment>
-    <comment ref="B23" authorId="0" shapeId="0">
+    <comment ref="B24" authorId="0" shapeId="0">
       <text>
         <t>The move you want the fees to cover.</t>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0">
+    <comment ref="B25" authorId="0" shapeId="0">
       <text>
         <t>How long the position is open.</t>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0">
+    <comment ref="B26" authorId="0" shapeId="0">
       <text>
         <t>Optional. Leave blank to see only the fee rate required.</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0">
+    <comment ref="B30" authorId="0" shapeId="0">
       <text>
         <t>Bottom of the range.</t>
       </text>
     </comment>
-    <comment ref="B30" authorId="0" shapeId="0">
+    <comment ref="B31" authorId="0" shapeId="0">
       <text>
         <t>Top of the range.</t>
       </text>
     </comment>
-    <comment ref="B33" authorId="0" shapeId="0">
+    <comment ref="B34" authorId="0" shapeId="0">
       <text>
         <t>Annualised volatility of the pair.</t>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0">
+    <comment ref="B35" authorId="0" shapeId="0">
       <text>
         <t>Fee APR you expect. Leave blank to see only LVR.</t>
       </text>
     </comment>
-    <comment ref="B37" authorId="0" shapeId="0">
+    <comment ref="B38" authorId="0" shapeId="0">
       <text>
         <t>What borrowers pay.</t>
       </text>
     </comment>
-    <comment ref="B38" authorId="0" shapeId="0">
+    <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>Share of deposits that is lent out.</t>
+        <t>Use 0 to 1. Share of deposits that is lent out.</t>
       </text>
     </comment>
-    <comment ref="B39" authorId="0" shapeId="0">
+    <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>Share of interest the protocol keeps.</t>
+        <t>Use 0 to 1. Share of interest the protocol keeps.</t>
       </text>
     </comment>
-    <comment ref="B42" authorId="0" shapeId="0">
+    <comment ref="B43" authorId="0" shapeId="0">
       <text>
         <t>The stated rate, before compounding.</t>
       </text>
     </comment>
-    <comment ref="B43" authorId="0" shapeId="0">
+    <comment ref="B44" authorId="0" shapeId="0">
       <text>
         <t>How often it compounds.</t>
       </text>
     </comment>
-    <comment ref="B44" authorId="0" shapeId="0">
+    <comment ref="B45" authorId="0" shapeId="0">
       <text>
         <t>Optional. Used only for the gas drag.</t>
       </text>
     </comment>
-    <comment ref="B45" authorId="0" shapeId="0">
+    <comment ref="B46" authorId="0" shapeId="0">
       <text>
         <t>Optional. What one compound costs.</t>
       </text>
     </comment>
-    <comment ref="B48" authorId="0" shapeId="0">
+    <comment ref="B49" authorId="0" shapeId="0">
       <text>
-        <t>Your estimate that the airdrop happens and you qualify.</t>
+        <t>Use 0 to 1. Your estimate that it happens and you qualify.</t>
       </text>
     </comment>
-    <comment ref="B49" authorId="0" shapeId="0">
+    <comment ref="B50" authorId="0" shapeId="0">
       <text>
         <t>What you could sell it for, not the headline.</t>
       </text>
     </comment>
-    <comment ref="B50" authorId="0" shapeId="0">
+    <comment ref="B51" authorId="0" shapeId="0">
       <text>
         <t>Gas, bridges, and time you count as a cost.</t>
       </text>
     </comment>
-    <comment ref="B53" authorId="0" shapeId="0">
+    <comment ref="B54" authorId="0" shapeId="0">
       <text>
         <t>0.95 means you pay 0.95 for a claim on 1 at maturity.</t>
       </text>
     </comment>
-    <comment ref="B54" authorId="0" shapeId="0">
+    <comment ref="B55" authorId="0" shapeId="0">
       <text>
         <t>Days left until redemption.</t>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B58" authorId="0" shapeId="0">
       <text>
         <t>Price of the asset today.</t>
       </text>
     </comment>
-    <comment ref="B58" authorId="0" shapeId="0">
+    <comment ref="B59" authorId="0" shapeId="0">
       <text>
         <t>Price of the dated future.</t>
       </text>
     </comment>
-    <comment ref="B59" authorId="0" shapeId="0">
+    <comment ref="B60" authorId="0" shapeId="0">
       <text>
         <t>Days until the future expires.</t>
       </text>
     </comment>
-    <comment ref="B62" authorId="0" shapeId="0">
+    <comment ref="B63" authorId="0" shapeId="0">
       <text>
         <t>Price of the asset you hold.</t>
       </text>
     </comment>
-    <comment ref="B63" authorId="0" shapeId="0">
+    <comment ref="B64" authorId="0" shapeId="0">
       <text>
         <t>The cap you are willing to sell at.</t>
       </text>
     </comment>
-    <comment ref="B64" authorId="0" shapeId="0">
+    <comment ref="B65" authorId="0" shapeId="0">
       <text>
         <t>Premium received, in percentage points of spot.</t>
       </text>
     </comment>
-    <comment ref="B65" authorId="0" shapeId="0">
+    <comment ref="B66" authorId="0" shapeId="0">
       <text>
         <t>Length of this option.</t>
       </text>
     </comment>
-    <comment ref="B68" authorId="0" shapeId="0">
+    <comment ref="B69" authorId="0" shapeId="0">
       <text>
         <t>The advertised rate, in percentage points.</t>
       </text>
     </comment>
-    <comment ref="B69" authorId="0" shapeId="0">
-      <text>
-        <t>Your assumed chance of a loss event this year.</t>
-      </text>
-    </comment>
     <comment ref="B70" authorId="0" shapeId="0">
       <text>
-        <t>Share of the position lost if that event happens.</t>
+        <t>Use 0 to 1. Your assumed chance of a loss event this year.</t>
       </text>
     </comment>
     <comment ref="B71" authorId="0" shapeId="0">
       <text>
+        <t>Use 0 to 1. Share of the position lost if that event happens.</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
         <t>Fees and gas, in percentage points.</t>
       </text>
     </comment>
-    <comment ref="B74" authorId="0" shapeId="0">
+    <comment ref="B75" authorId="0" shapeId="0">
       <text>
         <t>Capital in the position.</t>
       </text>
     </comment>
-    <comment ref="B75" authorId="0" shapeId="0">
+    <comment ref="B76" authorId="0" shapeId="0">
       <text>
         <t>Yield after the expected-loss haircut.</t>
       </text>
     </comment>
-    <comment ref="B76" authorId="0" shapeId="0">
+    <comment ref="B77" authorId="0" shapeId="0">
       <text>
-        <t>Share of expected income you pay out.</t>
+        <t>Use 0 to 1. Share of expected income you pay out.</t>
       </text>
     </comment>
-    <comment ref="B80" authorId="0" shapeId="0">
+    <comment ref="B81" authorId="0" shapeId="0">
       <text>
         <t>Collateral value.</t>
       </text>
     </comment>
-    <comment ref="B81" authorId="0" shapeId="0">
+    <comment ref="B82" authorId="0" shapeId="0">
       <text>
         <t>Cash you can reach quickly.</t>
       </text>
     </comment>
-    <comment ref="B82" authorId="0" shapeId="0">
+    <comment ref="B83" authorId="0" shapeId="0">
       <text>
         <t>Anything else you count.</t>
       </text>
     </comment>
-    <comment ref="B83" authorId="0" shapeId="0">
+    <comment ref="B84" authorId="0" shapeId="0">
       <text>
         <t>What you owe.</t>
       </text>
     </comment>
-    <comment ref="B84" authorId="0" shapeId="0">
+    <comment ref="B85" authorId="0" shapeId="0">
       <text>
         <t>Interest rate on the debt.</t>
       </text>
     </comment>
-    <comment ref="B85" authorId="0" shapeId="0">
+    <comment ref="B86" authorId="0" shapeId="0">
       <text>
         <t>Spending the reserve must also cover.</t>
       </text>
     </comment>
-    <comment ref="B86" authorId="0" shapeId="0">
+    <comment ref="B87" authorId="0" shapeId="0">
       <text>
-        <t>Threshold used for the health factor. 0.80 means 80%.</t>
+        <t>Use 0 to 1. 0.80 means 80%.</t>
       </text>
     </comment>
-    <comment ref="B87" authorId="0" shapeId="0">
+    <comment ref="B88" authorId="0" shapeId="0">
       <text>
-        <t>The cap from the lesson. 0.30 means 30%.</t>
+        <t>Use 0 to 1. 0.30 means 30%.</t>
       </text>
     </comment>
-    <comment ref="B90" authorId="0" shapeId="0">
+    <comment ref="B91" authorId="0" shapeId="0">
       <text>
         <t>Price you entered at.</t>
       </text>
     </comment>
-    <comment ref="B91" authorId="0" shapeId="0">
+    <comment ref="B92" authorId="0" shapeId="0">
       <text>
         <t>Isolated leverage.</t>
       </text>
     </comment>
-    <comment ref="B92" authorId="0" shapeId="0">
+    <comment ref="B93" authorId="0" shapeId="0">
       <text>
         <t>Type 1 for a long or -1 for a short.</t>
       </text>
     </comment>
-    <comment ref="B93" authorId="0" shapeId="0">
+    <comment ref="B94" authorId="0" shapeId="0">
       <text>
         <t>Maintenance margin, in percentage points.</t>
       </text>
     </comment>
-    <comment ref="B96" authorId="0" shapeId="0">
+    <comment ref="B97" authorId="0" shapeId="0">
       <text>
         <t>First period, in percentage points. Negative is allowed.</t>
       </text>
     </comment>
-    <comment ref="B97" authorId="0" shapeId="0">
+    <comment ref="B98" authorId="0" shapeId="0">
       <text>
         <t>Second period.</t>
       </text>
     </comment>
-    <comment ref="B98" authorId="0" shapeId="0">
+    <comment ref="B99" authorId="0" shapeId="0">
       <text>
         <t>Third period. Leave later periods blank.</t>
       </text>
     </comment>
-    <comment ref="B99" authorId="0" shapeId="0">
+    <comment ref="B100" authorId="0" shapeId="0">
       <text>
         <t>Optional.</t>
       </text>
     </comment>
-    <comment ref="B102" authorId="0" shapeId="0">
+    <comment ref="B103" authorId="0" shapeId="0">
       <text>
         <t>Units of collateral.</t>
       </text>
     </comment>
-    <comment ref="B103" authorId="0" shapeId="0">
+    <comment ref="B104" authorId="0" shapeId="0">
       <text>
         <t>Price per unit.</t>
       </text>
     </comment>
-    <comment ref="B104" authorId="0" shapeId="0">
+    <comment ref="B105" authorId="0" shapeId="0">
       <text>
         <t>Amount you mint.</t>
       </text>
     </comment>
-    <comment ref="B105" authorId="0" shapeId="0">
+    <comment ref="B106" authorId="0" shapeId="0">
       <text>
         <t>150 means 150%.</t>
       </text>
     </comment>
-    <comment ref="B106" authorId="0" shapeId="0">
+    <comment ref="B107" authorId="0" shapeId="0">
       <text>
         <t>Annual fee on the minted amount.</t>
       </text>
     </comment>
-    <comment ref="B109" authorId="0" shapeId="0">
+    <comment ref="B110" authorId="0" shapeId="0">
       <text>
         <t>The funding rate for one 8-hour period.</t>
       </text>
     </comment>
-    <comment ref="B110" authorId="0" shapeId="0">
+    <comment ref="B111" authorId="0" shapeId="0">
       <text>
         <t>Leverage on the short leg.</t>
       </text>
     </comment>
-    <comment ref="B114" authorId="0" shapeId="0">
+    <comment ref="B115" authorId="0" shapeId="0">
       <text>
         <t>Size of the position.</t>
       </text>
     </comment>
-    <comment ref="B115" authorId="0" shapeId="0">
+    <comment ref="B116" authorId="0" shapeId="0">
       <text>
         <t>Annualised volatility.</t>
       </text>
     </comment>
-    <comment ref="B116" authorId="0" shapeId="0">
+    <comment ref="B117" authorId="0" shapeId="0">
       <text>
         <t>1.65 is about a 95% one-day estimate. 2.33 is about 99%.</t>
       </text>
@@ -879,7 +903,7 @@
     </comment>
     <comment ref="B14" authorId="0" shapeId="0">
       <text>
-        <t>0.80 means 80%.</t>
+        <t>Use 0 to 1. 0.80 means 80%.</t>
       </text>
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
@@ -904,12 +928,42 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
-        <t>0.30 means 30%, the lesson cap. Compared with W6 LTV.</t>
+        <t>Use 0 to 1. 0.30 means 30%, the lesson cap. Compared with W6 LTV.</t>
       </text>
     </comment>
     <comment ref="B6" authorId="0" shapeId="0">
       <text>
         <t>The lesson floor is 2.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>On-Chain Operator Program</author>
+  </authors>
+  <commentList>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Use 0 to 1. 0.70 means you pay out 70% of expected income.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>On-Chain Operator Program</author>
+  </authors>
+  <commentList>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>50 means a 50% move. An illustration, not a forecast.</t>
       </text>
     </comment>
   </commentList>
@@ -1209,10 +1263,10 @@
   <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1244,7 +1298,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>What you do with it</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1252,310 +1306,405 @@
           <t>Lesson</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>When you open it</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>W1 Records</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0 · Zero</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>From the first action. One line each, and you keep the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>W3 Due diligence</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>3 · Analyst</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Module 6</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Before you use a protocol. Six checks, then a verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>W5 Portfolio</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>4 · Strategist</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>When you set the buckets. Targets should add to 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>W4 Risk register</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>4 · Strategist</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>When you score a risk. 20 or higher: do not hold it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>W2 Journal</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>4 · Strategist</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>When a position is open. Thesis, kill rules, weekly result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>W12 Stress test</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>4 · Strategist</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Before you size the book up. Five named scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>W13 Incident</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>4 · Strategist</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Before you need it. Channels and roles. No keys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>W6 Balance sheet</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>When you build the bank. Equity, LTV, health factor, runway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>W7 Custody</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>With the bank. Vault, operating wallet, hot float. No secrets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>W8 Credit policy</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>With the bank. The checks read the balance sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>W9 Liquidity</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>With the bank. Cash by how fast you can reach it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>W10 Lending</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>With the bank. Your assumed loss on each market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>W17 Letter</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>With the bank. Store it apart from any key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>W11 Income</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Module 13</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>When you set a payout from expected income, not the headline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>W16 Annual review</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Once a year. Equity, income, and whether the drill happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>W14 Alerts</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>When you automate watching. A threshold and an action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>W15 Automation</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>5 · Operator</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>When a bot can move funds. Write the cap and how you revoke it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Change a yellow number and read the green answer. Same formulas as the course calculators.</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Lessons 2–14</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>W1 Records</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Log every buy, sell, transfer, swap, fee, and income line.</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>W2 Journal</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>One row per position: thesis, kill rules, and the weekly result.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>W3 Due diligence</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Walk a protocol through the six checks before you use it.</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Module 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>W4 Risk register</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Score likelihood times impact. A score of 20 or more is a don't-hold.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>W5 Portfolio</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Set bucket targets. The sheet adds them up and flags a total that is not 100%.</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>W6 Balance sheet</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Enter assets and liabilities. Equity, LTV, health factor, and runway calculate.</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>W7 Custody</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Write the policy: vault, operating wallet, hot float, and a recovery test. No secrets.</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>W8 Credit policy</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Set the LTV cap and the health-factor floor, then check them against W6.</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>W9 Liquidity</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Ladder cash by how fast you can reach it, and see the gap to each target.</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>W10 Lending</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Record each market and its assumed loss. Expected loss calculates.</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>W11 Income</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>List positions. The sheet blends the risk-adjusted yield and the payout.</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Module 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>W12 Stress test</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Five scenarios are already named. You fill the loss and the fix.</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>W13 Incident</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Official channel, containment, and who you call. Roles, not keys.</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>W14 Alerts</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Threshold, tool, and the action you will take.</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>W15 Automation</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>What each bot is allowed to do, the cap, and how you revoke it.</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>W16 Annual review</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Start and end equity, income against the plan, and whether the drill happened.</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>W17 Letter</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Instructions for an executor. Store it apart from any key. No seeds.</t>
-        </is>
-      </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>Calculators</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Any time a lesson has a number. Yellow in, green answer.</t>
         </is>
       </c>
     </row>
@@ -1617,38 +1766,38 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A5:C23"/>
+  <autoFilter ref="A5:D23"/>
   <mergeCells count="10">
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A6" location="'Tools'!A1" tooltip="Change a yellow number and read the green answer. Same formulas as the course calculators."/>
-    <hyperlink ref="A7" location="'W1 Records'!A1" tooltip="Log every buy, sell, transfer, swap, fee, and income line."/>
-    <hyperlink ref="A8" location="'W2 Journal'!A1" tooltip="One row per position: thesis, kill rules, and the weekly result."/>
-    <hyperlink ref="A9" location="'W3 Due diligence'!A1" tooltip="Walk a protocol through the six checks before you use it."/>
-    <hyperlink ref="A10" location="'W4 Risk register'!A1" tooltip="Score likelihood times impact. A score of 20 or more is a don't-hold."/>
-    <hyperlink ref="A11" location="'W5 Portfolio'!A1" tooltip="Set bucket targets. The sheet adds them up and flags a total that is not 100%."/>
-    <hyperlink ref="A12" location="'W6 Balance sheet'!A1" tooltip="Enter assets and liabilities. Equity, LTV, health factor, and runway calculate."/>
-    <hyperlink ref="A13" location="'W7 Custody'!A1" tooltip="Write the policy: vault, operating wallet, hot float, and a recovery test. No secrets."/>
-    <hyperlink ref="A14" location="'W8 Credit policy'!A1" tooltip="Set the LTV cap and the health-factor floor, then check them against W6."/>
-    <hyperlink ref="A15" location="'W9 Liquidity'!A1" tooltip="Ladder cash by how fast you can reach it, and see the gap to each target."/>
-    <hyperlink ref="A16" location="'W10 Lending'!A1" tooltip="Record each market and its assumed loss. Expected loss calculates."/>
-    <hyperlink ref="A17" location="'W11 Income'!A1" tooltip="List positions. The sheet blends the risk-adjusted yield and the payout."/>
-    <hyperlink ref="A18" location="'W12 Stress test'!A1" tooltip="Five scenarios are already named. You fill the loss and the fix."/>
-    <hyperlink ref="A19" location="'W13 Incident'!A1" tooltip="Official channel, containment, and who you call. Roles, not keys."/>
-    <hyperlink ref="A20" location="'W14 Alerts'!A1" tooltip="Threshold, tool, and the action you will take."/>
-    <hyperlink ref="A21" location="'W15 Automation'!A1" tooltip="What each bot is allowed to do, the cap, and how you revoke it."/>
-    <hyperlink ref="A22" location="'W16 Annual review'!A1" tooltip="Start and end equity, income against the plan, and whether the drill happened."/>
-    <hyperlink ref="A23" location="'W17 Letter'!A1" tooltip="Instructions for an executor. Store it apart from any key. No seeds."/>
+    <hyperlink ref="A6" location="'W1 Records'!A1" tooltip="From the first action. One line each, and you keep the sheet."/>
+    <hyperlink ref="A7" location="'W3 Due diligence'!A1" tooltip="Before you use a protocol. Six checks, then a verdict."/>
+    <hyperlink ref="A8" location="'W5 Portfolio'!A1" tooltip="When you set the buckets. Targets should add to 100%."/>
+    <hyperlink ref="A9" location="'W4 Risk register'!A1" tooltip="When you score a risk. 20 or higher: do not hold it."/>
+    <hyperlink ref="A10" location="'W2 Journal'!A1" tooltip="When a position is open. Thesis, kill rules, weekly result."/>
+    <hyperlink ref="A11" location="'W12 Stress test'!A1" tooltip="Before you size the book up. Five named scenarios."/>
+    <hyperlink ref="A12" location="'W13 Incident'!A1" tooltip="Before you need it. Channels and roles. No keys."/>
+    <hyperlink ref="A13" location="'W6 Balance sheet'!A1" tooltip="When you build the bank. Equity, LTV, health factor, runway."/>
+    <hyperlink ref="A14" location="'W7 Custody'!A1" tooltip="With the bank. Vault, operating wallet, hot float. No secrets."/>
+    <hyperlink ref="A15" location="'W8 Credit policy'!A1" tooltip="With the bank. The checks read the balance sheet."/>
+    <hyperlink ref="A16" location="'W9 Liquidity'!A1" tooltip="With the bank. Cash by how fast you can reach it."/>
+    <hyperlink ref="A17" location="'W10 Lending'!A1" tooltip="With the bank. Your assumed loss on each market."/>
+    <hyperlink ref="A18" location="'W17 Letter'!A1" tooltip="With the bank. Store it apart from any key."/>
+    <hyperlink ref="A19" location="'W11 Income'!A1" tooltip="When you set a payout from expected income, not the headline."/>
+    <hyperlink ref="A20" location="'W16 Annual review'!A1" tooltip="Once a year. Equity, income, and whether the drill happened."/>
+    <hyperlink ref="A21" location="'W14 Alerts'!A1" tooltip="When you automate watching. A threshold and an action."/>
+    <hyperlink ref="A22" location="'W15 Automation'!A1" tooltip="When a bot can move funds. Write the cap and how you revoke it."/>
+    <hyperlink ref="A23" location="'Tools'!A1" tooltip="Any time a lesson has a number. Yellow in, green answer."/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1"/>
@@ -1699,99 +1848,99 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Max LTV (0 to 1)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="19" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Health-factor floor</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="19" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Alert level 1</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
+      <c r="B7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Action at alert 1</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n"/>
+      <c r="B8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Alert level 2</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
+      <c r="B9" s="19" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Action at alert 2</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
+      <c r="B10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Fixed or variable, and why</t>
         </is>
       </c>
-      <c r="B11" s="38" t="n"/>
+      <c r="B11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Repayment source</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n"/>
+      <c r="B12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Collateral you allow</t>
         </is>
       </c>
-      <c r="B13" s="38" t="n"/>
+      <c r="B13" s="41" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>W6 LTV is within this cap</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="25">
         <f>IF(OR(B5="",'W6 Balance sheet'!B21=""),"",IF('W6 Balance sheet'!B21&lt;=B5,"Yes","No"))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>W6 health factor is at or above the floor</t>
         </is>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="25">
         <f>IF(OR(B6="",'W6 Balance sheet'!B22=""),"",IF('W6 Balance sheet'!B22&gt;=B6,"Yes","No"))</f>
         <v/>
       </c>
@@ -1803,6 +1952,12 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use 0 to 1" error="Enter a number from 0 to 1. 0.80 means 80%." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1832,7 +1987,7 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1884,12 +2039,12 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Gap (above 0 is short)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
@@ -1899,16 +2054,16 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="C5" s="38" t="n"/>
-      <c r="D5" s="45" t="n"/>
-      <c r="E5" s="45" t="n"/>
-      <c r="F5" s="29">
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="48" t="n"/>
+      <c r="E5" s="48" t="n"/>
+      <c r="F5" s="32">
         <f>IF(OR(D5="",E5=""),"",D5-E5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -1918,16 +2073,16 @@
           <t>Hours</t>
         </is>
       </c>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="29">
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="48" t="n"/>
+      <c r="E6" s="48" t="n"/>
+      <c r="F6" s="32">
         <f>IF(OR(D6="",E6=""),"",D6-E6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -1937,16 +2092,16 @@
           <t>Scheduled</t>
         </is>
       </c>
-      <c r="C7" s="38" t="n"/>
-      <c r="D7" s="45" t="n"/>
-      <c r="E7" s="45" t="n"/>
-      <c r="F7" s="29">
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="48" t="n"/>
+      <c r="E7" s="48" t="n"/>
+      <c r="F7" s="32">
         <f>IF(OR(D7="",E7=""),"",D7-E7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -1956,24 +2111,24 @@
           <t>Days–weeks</t>
         </is>
       </c>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="45" t="n"/>
-      <c r="E8" s="45" t="n"/>
-      <c r="F8" s="29">
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="48" t="n"/>
+      <c r="E8" s="48" t="n"/>
+      <c r="F8" s="32">
         <f>IF(OR(D8="",E8=""),"",D8-E8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Refill rule</t>
         </is>
       </c>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="42" t="n"/>
-      <c r="E10" s="42" t="n"/>
-      <c r="F10" s="43" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="45" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -1984,6 +2139,11 @@
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <conditionalFormatting sqref="F5:F8">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2087,172 +2247,172 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="n"/>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="46" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="46" t="n"/>
-      <c r="G5" s="46" t="n"/>
-      <c r="H5" s="21">
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="49" t="n"/>
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="23">
         <f>IF(OR(F5="",G5=""),"",F5*G5)</f>
         <v/>
       </c>
-      <c r="I5" s="47" t="n"/>
+      <c r="I5" s="50" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="46" t="n"/>
-      <c r="G6" s="46" t="n"/>
-      <c r="H6" s="21">
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="23">
         <f>IF(OR(F6="",G6=""),"",F6*G6)</f>
         <v/>
       </c>
-      <c r="I6" s="47" t="n"/>
+      <c r="I6" s="50" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="46" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="46" t="n"/>
-      <c r="G7" s="46" t="n"/>
-      <c r="H7" s="21">
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="23">
         <f>IF(OR(F7="",G7=""),"",F7*G7)</f>
         <v/>
       </c>
-      <c r="I7" s="47" t="n"/>
+      <c r="I7" s="50" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="46" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="46" t="n"/>
-      <c r="G8" s="46" t="n"/>
-      <c r="H8" s="21">
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="23">
         <f>IF(OR(F8="",G8=""),"",F8*G8)</f>
         <v/>
       </c>
-      <c r="I8" s="47" t="n"/>
+      <c r="I8" s="50" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="46" t="n"/>
-      <c r="G9" s="46" t="n"/>
-      <c r="H9" s="21">
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="23">
         <f>IF(OR(F9="",G9=""),"",F9*G9)</f>
         <v/>
       </c>
-      <c r="I9" s="47" t="n"/>
+      <c r="I9" s="50" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="46" t="n"/>
-      <c r="G10" s="46" t="n"/>
-      <c r="H10" s="21">
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="23">
         <f>IF(OR(F10="",G10=""),"",F10*G10)</f>
         <v/>
       </c>
-      <c r="I10" s="47" t="n"/>
+      <c r="I10" s="50" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="46" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="46" t="n"/>
-      <c r="G11" s="46" t="n"/>
-      <c r="H11" s="21">
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="23">
         <f>IF(OR(F11="",G11=""),"",F11*G11)</f>
         <v/>
       </c>
-      <c r="I11" s="47" t="n"/>
+      <c r="I11" s="50" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="21">
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="23">
         <f>IF(OR(F12="",G12=""),"",F12*G12)</f>
         <v/>
       </c>
-      <c r="I12" s="47" t="n"/>
+      <c r="I12" s="50" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-      <c r="H13" s="21">
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="23">
         <f>IF(OR(F13="",G13=""),"",F13*G13)</f>
         <v/>
       </c>
-      <c r="I13" s="47" t="n"/>
+      <c r="I13" s="50" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="21">
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="23">
         <f>IF(OR(F14="",G14=""),"",F14*G14)</f>
         <v/>
       </c>
-      <c r="I14" s="47" t="n"/>
+      <c r="I14" s="50" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="46" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-      <c r="H15" s="21">
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="23">
         <f>IF(OR(F15="",G15=""),"",F15*G15)</f>
         <v/>
       </c>
-      <c r="I15" s="47" t="n"/>
+      <c r="I15" s="50" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="46" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-      <c r="H16" s="21">
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="23">
         <f>IF(OR(F16="",G16=""),"",F16*G16)</f>
         <v/>
       </c>
-      <c r="I16" s="47" t="n"/>
+      <c r="I16" s="50" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -2262,6 +2422,12 @@
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use 0 to 1" error="Enter a number from 0 to 1. 0.80 means 80%." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2353,303 +2519,303 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Stable lending A</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="39" t="n">
         <v>100000</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="46" t="n">
+      <c r="D5" s="49" t="n">
         <v>0.005</v>
       </c>
-      <c r="E5" s="46" t="n">
+      <c r="E5" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="28">
         <f>IF(C5="","",C5-D5*E5*100)</f>
         <v/>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>IF(OR(B5="",F5=""),"",B5*F5/100)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Stable lending B</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="39" t="n">
         <v>100000</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="51" t="n">
         <v>4.5</v>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="49" t="n">
         <v>0.005</v>
       </c>
-      <c r="E6" s="46" t="n">
+      <c r="E6" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="28">
         <f>IF(C6="","",C6-D6*E6*100)</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="21">
         <f>IF(OR(B6="",F6=""),"",B6*F6/100)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>LST staking</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="39" t="n">
         <v>150000</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="51" t="n">
         <v>3.2</v>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="49" t="n">
         <v>0.01</v>
       </c>
-      <c r="E7" s="46" t="n">
+      <c r="E7" s="49" t="n">
         <v>0.5</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="28">
         <f>IF(C7="","",C7-D7*E7*100)</f>
         <v/>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="21">
         <f>IF(OR(B7="",F7=""),"",B7*F7/100)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>PT fixed stable</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="39" t="n">
         <v>100000</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="49" t="n">
         <v>0.02</v>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="49" t="n">
         <v>0.5</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="28">
         <f>IF(C8="","",C8-D8*E8*100)</f>
         <v/>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="21">
         <f>IF(OR(B8="",F8=""),"",B8*F8/100)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Funding carry</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="39" t="n">
         <v>50000</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="49" t="n">
         <v>0.05</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="49" t="n">
         <v>0.3</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="28">
         <f>IF(C9="","",C9-D9*E9*100)</f>
         <v/>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="21">
         <f>IF(OR(B9="",F9=""),"",B9*F9/100)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="37" t="n"/>
-      <c r="C10" s="48" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="46" t="n"/>
-      <c r="F10" s="25">
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="51" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="28">
         <f>IF(C10="","",C10-D10*E10*100)</f>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="21">
         <f>IF(OR(B10="",F10=""),"",B10*F10/100)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="37" t="n"/>
-      <c r="C11" s="48" t="n"/>
-      <c r="D11" s="46" t="n"/>
-      <c r="E11" s="46" t="n"/>
-      <c r="F11" s="25">
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="51" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="28">
         <f>IF(C11="","",C11-D11*E11*100)</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="21">
         <f>IF(OR(B11="",F11=""),"",B11*F11/100)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="37" t="n"/>
-      <c r="C12" s="48" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="25">
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="39" t="n"/>
+      <c r="C12" s="51" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="28">
         <f>IF(C12="","",C12-D12*E12*100)</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="21">
         <f>IF(OR(B12="",F12=""),"",B12*F12/100)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="37" t="n"/>
-      <c r="C13" s="48" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="25">
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="39" t="n"/>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="28">
         <f>IF(C13="","",C13-D13*E13*100)</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="21">
         <f>IF(OR(B13="",F13=""),"",B13*F13/100)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="48" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="25">
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="28">
         <f>IF(C14="","",C14-D14*E14*100)</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="21">
         <f>IF(OR(B14="",F14=""),"",B14*F14/100)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="21">
         <f>SUM(B5:B14)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Expected income per year</t>
         </is>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="21">
         <f>SUM(G5:G14)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Blended risk-adjusted yield</t>
         </is>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="28">
         <f>IF(B16=0,"",G17/B16*100)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Payout ratio (0 to 1)</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="19" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Payout per year</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="21">
         <f>IF(B20="","",G17*B20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Payout per month</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="21">
         <f>IF(B21="","",B21/12)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Retained as a buffer</t>
         </is>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="21">
         <f>IF(B21="","",G17-B21)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Review rule</t>
         </is>
       </c>
-      <c r="B25" s="38" t="n"/>
-      <c r="C25" s="42" t="n"/>
-      <c r="D25" s="42" t="n"/>
-      <c r="E25" s="42" t="n"/>
-      <c r="F25" s="42" t="n"/>
-      <c r="G25" s="43" t="n"/>
+      <c r="B25" s="41" t="n"/>
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+      <c r="F25" s="44" t="n"/>
+      <c r="G25" s="45" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -2660,6 +2826,12 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B25:G25"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B20 D5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use 0 to 1" error="Enter a number from 0 to 1. 0.80 means 80%." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2670,6 +2842,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2680,11 +2853,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -2745,71 +2918,106 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Crypto −50%</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="38" t="n"/>
-      <c r="D5" s="38" t="n"/>
-      <c r="E5" s="38" t="n"/>
-      <c r="F5" s="38" t="n"/>
+      <c r="B5" s="52" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Stablecoin −10%</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n"/>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Borrow rate 20%</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n"/>
-      <c r="C7" s="38" t="n"/>
-      <c r="D7" s="38" t="n"/>
-      <c r="E7" s="38" t="n"/>
-      <c r="F7" s="38" t="n"/>
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Largest protocol hacked</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n"/>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n"/>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Main L2 halted 48h</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n"/>
-      <c r="C9" s="38" t="n"/>
-      <c r="D9" s="38" t="n"/>
-      <c r="E9" s="38" t="n"/>
-      <c r="F9" s="38" t="n"/>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="41" t="n"/>
+      <c r="F9" s="41" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio value, for an illustration</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Shock, in percentage points</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Illustrative dollar loss</t>
+        </is>
+      </c>
+      <c r="B13" s="54">
+        <f>IF(OR(B11="",B12=""),"",B11*B12/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t>Put that dollar figure in the Loss column as a starting point, then write the fix.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A4:F5"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
@@ -2827,6 +3035,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2902,84 +3111,84 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="n"/>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="37" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="37" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -3062,100 +3271,100 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="n"/>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="35" t="n"/>
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="37" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -3250,100 +3459,100 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="n"/>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="37" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="37" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="37" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="37" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -3373,7 +3582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3404,180 +3613,191 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Equity at the start</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
+      <c r="B5" s="22" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Equity at the end</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n"/>
+      <c r="B6" s="22" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Change in equity</t>
+        </is>
+      </c>
+      <c r="B7" s="21">
+        <f>IF(OR(B5="",B6=""),"",B6-B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>LTV at the review</t>
         </is>
       </c>
-      <c r="B7" s="50" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="B8" s="53" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Runway at the review (months)</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="B9" s="48" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Payout paid</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="B10" s="22" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Payout the policy allowed</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="B11" s="22" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Payout versus policy</t>
         </is>
       </c>
-      <c r="B11" s="19">
-        <f>IF(OR(B9="",B10=""),"",B9-B10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B12" s="21">
+        <f>IF(OR(B10="",B11=""),"",B10-B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Income expected</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Income realised</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="19">
-        <f>IF(OR(B14="",C14=""),"",C14-B14)</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="37" t="n"/>
-      <c r="C15" s="37" t="n"/>
-      <c r="D15" s="19">
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="39" t="n"/>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="21">
         <f>IF(OR(B15="",C15=""),"",C15-B15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="37" t="n"/>
-      <c r="C16" s="37" t="n"/>
-      <c r="D16" s="19">
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="39" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="21">
         <f>IF(OR(B16="",C16=""),"",C16-B16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="37" t="n"/>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="19">
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="39" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="21">
         <f>IF(OR(B17="",C17=""),"",C17-B17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="19">
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="39" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="21">
         <f>IF(OR(B18="",C18=""),"",C18-B18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="37" t="n"/>
-      <c r="C19" s="37" t="n"/>
-      <c r="D19" s="19">
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="39" t="n"/>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="21">
         <f>IF(OR(B19="",C19=""),"",C19-B19)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="39" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="21">
+        <f>IF(OR(B20="",C20=""),"",C20-B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Losses and near-misses</t>
         </is>
       </c>
-      <c r="B21" s="38" t="n"/>
-      <c r="C21" s="42" t="n"/>
-      <c r="D21" s="43" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="B22" s="41" t="n"/>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="45" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Updated loss assumptions</t>
         </is>
       </c>
-      <c r="B22" s="38" t="n"/>
-      <c r="C22" s="42" t="n"/>
-      <c r="D22" s="43" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="B23" s="41" t="n"/>
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="45" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Custody and succession drill done?</t>
         </is>
       </c>
-      <c r="B23" s="38" t="n"/>
+      <c r="B24" s="41" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A13:D19"/>
+  <autoFilter ref="A14:D20"/>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3630,60 +3850,60 @@
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Wallet types that exist (hardware, multisig, hot). Not the keys.</t>
         </is>
       </c>
-      <c r="B5" s="38" t="n"/>
+      <c r="B5" s="41" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Multisig shape (for example 2 of 3) and the roles, not the people's secrets.</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n"/>
+      <c r="B6" s="41" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Where the documents are (this file, the journal, the due-diligence notes).</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n"/>
+      <c r="B7" s="41" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Co-signer or professional, by name and role.</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n"/>
+      <c r="B8" s="41" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>How the executor should proceed, in order.</t>
         </is>
       </c>
-      <c r="B9" s="38" t="n"/>
+      <c r="B9" s="41" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Who to call first.</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
+      <c r="B10" s="41" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>What not to do.</t>
         </is>
       </c>
-      <c r="B11" s="38" t="n"/>
+      <c r="B11" s="41" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -3712,7 +3932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3720,6 +3940,7 @@
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3764,1337 +3985,1498 @@
           <t>Green formula</t>
         </is>
       </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Jump to a calculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Health factor and liquidation price</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Health factor and liquidation price   ·   Lesson 3.2</t>
         </is>
       </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Leveraged loop</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Collateral quantity</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Collateral value</t>
         </is>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="21">
         <f>B7*B8</f>
         <v/>
       </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Impermanent loss vs holding</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Collateral price</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>LTV</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="23">
         <f>IF(B7*B8=0,"",B10/(B7*B8))</f>
         <v/>
       </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>LP fee breakeven</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Liquidation threshold (0 to 1)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="19" t="n">
         <v>0.8</v>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Health factor</t>
         </is>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="24">
         <f>IF(B10=0,"",B7*B8*B9/B10)</f>
         <v/>
       </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Concentrated liquidity efficiency</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Liquidation price</t>
         </is>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="21">
         <f>IF(B7*B9=0,"",B10/(B7*B9))</f>
         <v/>
       </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Loss versus rebalancing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Max debt for HF 2</t>
         </is>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="21">
         <f>IF(B9=0,"",B7*B8*B9/2)</f>
         <v/>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Lending supply APY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Check against 1.5</t>
+        </is>
+      </c>
+      <c r="E12" s="25">
+        <f>IF(E9="","",IF(E9&lt;1.5,"Below 1.5: repay or add collateral","At or above 1.5"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>APR, APY, and gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>Airdrop expected value</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Leveraged loop   ·   Lesson 3.4</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Principal token fixed yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Borrow LTV (0 to 1)</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B15" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Leverage</t>
         </is>
       </c>
-      <c r="E14" s="23">
-        <f>IF(OR(B14&lt;=0,B14&gt;=1),"", (1-B14^(B15+1))/(1-B14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="E15" s="26">
+        <f>IF(OR(B15&lt;=0,B15&gt;=1),"", (1-B15^(B16+1))/(1-B15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>Cash-and-carry basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Loops</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B16" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Net APY on equity</t>
         </is>
       </c>
-      <c r="E15" s="25">
-        <f>IF(OR(B14&lt;=0,B14&gt;=1),"",B16*E14-B17*(E14-1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="E16" s="28">
+        <f>IF(OR(B15&lt;=0,B15&gt;=1),"",B17*E15-B18*(E15-1))</f>
+        <v/>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>Covered call</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Collateral APY</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B17" s="29" t="n">
         <v>3.5</v>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Breakeven borrow APY</t>
         </is>
       </c>
-      <c r="E16" s="25">
-        <f>IF(OR(E14="",E14&lt;=1),"",B16*E14/(E14-1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="E17" s="28">
+        <f>IF(OR(E15="",E15&lt;=1),"",B17*E15/(E15-1))</f>
+        <v/>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>Risk-adjusted yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Borrow APY</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B18" s="29" t="n">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>What the leverage did</t>
+        </is>
+      </c>
+      <c r="E18" s="25">
+        <f>IF(E16="","",IF(E16&lt;=B17,"Adds nothing: the borrow rate is too high","Adds a spread over the unlevered yield"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>Income and payout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>Balance sheet check</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Impermanent loss vs holding   ·   Lesson 2.4</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>Perp liquidation price</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Price ratio (end ÷ start)</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B21" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>IL vs holding</t>
         </is>
       </c>
-      <c r="E20" s="25">
-        <f>((2*SQRT(B20)/(1+B20))-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="E21" s="28">
+        <f>((2*SQRT(B21)/(1+B21))-1)*100</f>
+        <v/>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>Time-weighted return</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>CDP mint</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>LP fee breakeven   ·   Lesson 2.4</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>Funding carry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Price ratio</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B24" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>IL over the period</t>
         </is>
       </c>
-      <c r="E23" s="25">
-        <f>-( (2*SQRT(B23)/(1+B23))-1 )*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="E24" s="28">
+        <f>-( (2*SQRT(B24)/(1+B24))-1 )*100</f>
+        <v/>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>One-day value at risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Days held</t>
         </is>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B25" s="27" t="n">
         <v>90</v>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>Fee APR to match holding</t>
         </is>
       </c>
-      <c r="E24" s="25">
-        <f>IF(B24=0,"",E23*365/B24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="E25" s="28">
+        <f>IF(B25=0,"",E24*365/B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Fee APR you expect</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B26" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Fees earned over the days</t>
         </is>
       </c>
-      <c r="E25" s="25">
-        <f>IF(B25="","",B25*B24/365)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="D26" s="18" t="inlineStr">
+      <c r="E26" s="28">
+        <f>IF(B26="","",B26*B25/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>Fees minus IL</t>
         </is>
       </c>
-      <c r="E26" s="25">
-        <f>IF(B25="","",E25-E23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="E27" s="28">
+        <f>IF(B26="","",E26-E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Concentrated liquidity efficiency   ·   Lesson 2.6</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Range low</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B30" s="22" t="n">
         <v>1800</v>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Geometric mid</t>
         </is>
       </c>
-      <c r="E29" s="19">
-        <f>IF(OR(B29&lt;=0,B30&lt;=B29),"",SQRT(B29*B30))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="E30" s="21">
+        <f>IF(OR(B30&lt;=0,B31&lt;=B30),"",SQRT(B30*B31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Range high</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B31" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>Capital efficiency vs full range</t>
         </is>
       </c>
-      <c r="E30" s="27">
-        <f>IF(OR(B29&lt;=0,B30&lt;=B29),"",1/(1-(B29/B30)^0.25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="E31" s="30">
+        <f>IF(OR(B30&lt;=0,B31&lt;=B30),"",1/(1-(B30/B31)^0.25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Loss versus rebalancing   ·   Lesson 2.7</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>Volatility per year</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B34" s="29" t="n">
         <v>80</v>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>LVR per year</t>
         </is>
       </c>
-      <c r="E33" s="25">
-        <f>(B33/100)^2/8*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="E34" s="28">
+        <f>(B34/100)^2/8*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Fee APR</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B35" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>Fees minus LVR</t>
         </is>
       </c>
-      <c r="E34" s="25">
-        <f>IF(B34="","",B34-E33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="E35" s="28">
+        <f>IF(B35="","",B35-E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Lending supply APY   ·   Lesson 4.2</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Borrow APY</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B38" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Supply APY</t>
         </is>
       </c>
-      <c r="E37" s="25">
-        <f>B37*B38*(1-B39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="E38" s="28">
+        <f>B38*B39*(1-B40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>Utilisation (0 to 1)</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B39" s="19" t="n">
         <v>0.8</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>Reserve factor (0 to 1)</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n">
+      <c r="B40" s="19" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>APR, APY, and gas   ·   Lesson 4.1</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="B42" s="26" t="n">
+      <c r="B43" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>APY before gas</t>
         </is>
       </c>
-      <c r="E42" s="25">
-        <f>IF(OR(B43&lt;=0),"",( (1+B42/100/B43)^B43 - 1)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="E43" s="28">
+        <f>IF(OR(B44&lt;=0),"",( (1+B43/100/B44)^B44 - 1)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Compounds per year</t>
         </is>
       </c>
-      <c r="B43" s="24" t="n">
+      <c r="B44" s="27" t="n">
         <v>365</v>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>Gas drag</t>
         </is>
       </c>
-      <c r="E43" s="25">
-        <f>IF(OR(B44="",B44=0,B45=""),"",B45*B43/B44*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="E44" s="28">
+        <f>IF(OR(B45="",B45=0,B46=""),"",B46*B44/B45*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>Position size</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B45" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="D44" s="18" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>APY after gas</t>
         </is>
       </c>
-      <c r="E44" s="25">
-        <f>IF(E43="","",E42-E43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="E45" s="28">
+        <f>IF(E44="","",E43-E44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Gas per compound</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
+      <c r="B46" s="22" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Airdrop expected value   ·   Lesson 4.6</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Probability (0 to 1)</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n">
+      <c r="B49" s="19" t="n">
         <v>0.3</v>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>Expected value</t>
         </is>
       </c>
-      <c r="E48" s="19">
-        <f>B48*B49-B50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="E49" s="21">
+        <f>B49*B50-B51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>Value if it happens</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n">
+      <c r="B50" s="22" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Costs</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n">
+      <c r="B51" s="22" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="15" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Principal token fixed yield   ·   Lesson 10.1</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>PT price (share of underlying)</t>
         </is>
       </c>
-      <c r="B53" s="17" t="n">
+      <c r="B54" s="19" t="n">
         <v>0.95</v>
       </c>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>Fixed APY if held</t>
         </is>
       </c>
-      <c r="E53" s="28">
-        <f>IF(OR(B53&lt;=0,B54=0),"",(B53^(-1))^(365/B54)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="E54" s="31">
+        <f>IF(OR(B54&lt;=0,B55=0),"",(B54^(-1))^(365/B55)-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Days to maturity</t>
         </is>
       </c>
-      <c r="B54" s="24" t="n">
+      <c r="B55" s="27" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="15" t="inlineStr">
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Cash-and-carry basis   ·   Lesson 10.3</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
         <is>
           <t>Spot price</t>
         </is>
       </c>
-      <c r="B57" s="20" t="n">
+      <c r="B58" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="D58" s="20" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E57" s="28">
-        <f>IF(B57=0,"",B58/B57-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="E58" s="31">
+        <f>IF(B58=0,"",B59/B58-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>Futures price</t>
         </is>
       </c>
-      <c r="B58" s="20" t="n">
+      <c r="B59" s="22" t="n">
         <v>3150</v>
       </c>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>Annualised, simple</t>
         </is>
       </c>
-      <c r="E58" s="28">
-        <f>IF(B59=0,"",E57*365/B59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="E59" s="31">
+        <f>IF(B60=0,"",E58*365/B60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>Days to expiry</t>
         </is>
       </c>
-      <c r="B59" s="24" t="n">
+      <c r="B60" s="27" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="15" t="inlineStr">
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Covered call   ·   Lesson 10.4</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t>Spot price</t>
         </is>
       </c>
-      <c r="B62" s="20" t="n">
+      <c r="B63" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="D62" s="18" t="inlineStr">
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>Annualised if repeated</t>
         </is>
       </c>
-      <c r="E62" s="25">
-        <f>IF(B65=0,"",B64*365/B65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="E63" s="28">
+        <f>IF(B66=0,"",B65*365/B66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
         <is>
           <t>Strike</t>
         </is>
       </c>
-      <c r="B63" s="20" t="n">
+      <c r="B64" s="22" t="n">
         <v>3300</v>
       </c>
-      <c r="D63" s="18" t="inlineStr">
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>Max gain this period</t>
         </is>
       </c>
-      <c r="E63" s="25">
-        <f>IF(B62=0,"",B64+(B63/B62-1)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="E64" s="28">
+        <f>IF(B63=0,"",B65+(B64/B63-1)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B64" s="26" t="n">
+      <c r="B65" s="29" t="n">
         <v>1.5</v>
       </c>
-      <c r="D64" s="18" t="inlineStr">
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>Break-even price</t>
         </is>
       </c>
-      <c r="E64" s="19">
-        <f>B62*(1-B64/100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="E65" s="21">
+        <f>B63*(1-B65/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>Days in the period</t>
         </is>
       </c>
-      <c r="B65" s="24" t="n">
+      <c r="B66" s="27" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="15" t="inlineStr">
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>Risk-adjusted yield   ·   Lesson 13.2</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>Headline yield</t>
         </is>
       </c>
-      <c r="B68" s="26" t="n">
+      <c r="B69" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="D68" s="18" t="inlineStr">
+      <c r="D69" s="20" t="inlineStr">
         <is>
           <t>Expected loss</t>
         </is>
       </c>
-      <c r="E68" s="25">
-        <f>B69*B70*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="E69" s="28">
+        <f>B70*B71*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>Loss probability (0 to 1)</t>
         </is>
       </c>
-      <c r="B69" s="17" t="n">
+      <c r="B70" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D70" s="20" t="inlineStr">
         <is>
           <t>Risk-adjusted result</t>
         </is>
       </c>
-      <c r="E69" s="25">
-        <f>B68-E68-B71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="E70" s="28">
+        <f>B69-E69-B72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>Loss given default (0 to 1)</t>
         </is>
       </c>
-      <c r="B70" s="17" t="n">
+      <c r="B71" s="19" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="16" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t>Other costs</t>
         </is>
       </c>
-      <c r="B71" s="26" t="n">
+      <c r="B72" s="29" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>Income and payout   ·   Module 13</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
         <is>
           <t>Position amount</t>
         </is>
       </c>
-      <c r="B74" s="20" t="n">
+      <c r="B75" s="22" t="n">
         <v>250000</v>
       </c>
-      <c r="D74" s="18" t="inlineStr">
+      <c r="D75" s="20" t="inlineStr">
         <is>
           <t>Expected income per year</t>
         </is>
       </c>
-      <c r="E74" s="19">
-        <f>B74*B75/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="16" t="inlineStr">
+      <c r="E75" s="21">
+        <f>B75*B76/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>Risk-adjusted yield</t>
         </is>
       </c>
-      <c r="B75" s="26" t="n">
+      <c r="B76" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="D75" s="18" t="inlineStr">
+      <c r="D76" s="20" t="inlineStr">
         <is>
           <t>Payout per year</t>
         </is>
       </c>
-      <c r="E75" s="19">
-        <f>E74*B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+      <c r="E76" s="21">
+        <f>E75*B77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="inlineStr">
         <is>
           <t>Payout ratio (0 to 1)</t>
         </is>
       </c>
-      <c r="B76" s="17" t="n">
+      <c r="B77" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="D76" s="18" t="inlineStr">
+      <c r="D77" s="20" t="inlineStr">
         <is>
           <t>Payout per month</t>
         </is>
       </c>
-      <c r="E76" s="19">
-        <f>E75/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="D77" s="18" t="inlineStr">
+      <c r="E77" s="21">
+        <f>E76/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" s="20" t="inlineStr">
         <is>
           <t>Retained as a buffer</t>
         </is>
       </c>
-      <c r="E77" s="19">
-        <f>E74-E75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="15" t="inlineStr">
+      <c r="E78" s="21">
+        <f>E75-E76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="17" t="inlineStr">
         <is>
           <t>Balance sheet check   ·   Lesson 12.1</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
         <is>
           <t>Collateral</t>
         </is>
       </c>
-      <c r="B80" s="20" t="n">
+      <c r="B81" s="22" t="n">
         <v>300000</v>
       </c>
-      <c r="D80" s="18" t="inlineStr">
+      <c r="D81" s="20" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="E80" s="19">
-        <f>B80+B81+B82-B83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+      <c r="E81" s="21">
+        <f>B81+B82+B83-B84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
         <is>
           <t>Reserve</t>
         </is>
       </c>
-      <c r="B81" s="20" t="n">
+      <c r="B82" s="22" t="n">
         <v>40000</v>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="D82" s="20" t="inlineStr">
         <is>
           <t>LTV</t>
         </is>
       </c>
-      <c r="E81" s="21">
-        <f>IF(B80=0,"",B83/B80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="16" t="inlineStr">
+      <c r="E82" s="23">
+        <f>IF(B81=0,"",B84/B81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr">
         <is>
           <t>Other assets</t>
         </is>
       </c>
-      <c r="B82" s="20" t="n">
+      <c r="B83" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="18" t="inlineStr">
+      <c r="D83" s="20" t="inlineStr">
         <is>
           <t>Health factor</t>
         </is>
       </c>
-      <c r="E82" s="22">
-        <f>IF(B83=0,"",B80*B86/B83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="16" t="inlineStr">
+      <c r="E83" s="24">
+        <f>IF(B84=0,"",B81*B87/B84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="B83" s="20" t="n">
+      <c r="B84" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="D83" s="18" t="inlineStr">
+      <c r="D84" s="20" t="inlineStr">
         <is>
           <t>Reserve runway (months)</t>
         </is>
       </c>
-      <c r="E83" s="29">
-        <f>IF((B85+B83*B84/100/12)=0,"",B81/(B85+B83*B84/100/12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="E84" s="32">
+        <f>IF((B86+B84*B85/100/12)=0,"",B82/(B86+B84*B85/100/12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
         <is>
           <t>Borrow APY</t>
         </is>
       </c>
-      <c r="B84" s="26" t="n">
+      <c r="B85" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="D84" s="18" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>LTV within policy</t>
         </is>
       </c>
-      <c r="E84" s="30">
-        <f>IF(E81="","",IF(E81&lt;=B87,"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="E85" s="25">
+        <f>IF(E82="","",IF(E82&lt;=B88,"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
         <is>
           <t>Monthly spending</t>
         </is>
       </c>
-      <c r="B85" s="20" t="n">
+      <c r="B86" s="22" t="n">
         <v>5000</v>
       </c>
-      <c r="D85" s="18" t="inlineStr">
+      <c r="D86" s="20" t="inlineStr">
         <is>
           <t>Health factor at least 2</t>
         </is>
       </c>
-      <c r="E85" s="30">
-        <f>IF(E82="","",IF(E82&gt;=2,"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+      <c r="E86" s="25">
+        <f>IF(E83="","",IF(E83&gt;=2,"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
         <is>
           <t>Liquidation threshold (0 to 1)</t>
         </is>
       </c>
-      <c r="B86" s="17" t="n">
+      <c r="B87" s="19" t="n">
         <v>0.8</v>
       </c>
-      <c r="D86" s="18" t="inlineStr">
+      <c r="D87" s="20" t="inlineStr">
         <is>
           <t>Reserve covers 6 months</t>
         </is>
       </c>
-      <c r="E86" s="30">
-        <f>IF(E83="","",IF(E83&gt;=6,"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+      <c r="E87" s="25">
+        <f>IF(E84="","",IF(E84&gt;=6,"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
         <is>
           <t>Max LTV policy (0 to 1)</t>
         </is>
       </c>
-      <c r="B87" s="17" t="n">
+      <c r="B88" s="19" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="15" t="inlineStr">
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t>Perp liquidation price   ·   Lesson 3.5</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="16" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>Entry price</t>
         </is>
       </c>
-      <c r="B90" s="20" t="n">
+      <c r="B91" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="D90" s="18" t="inlineStr">
+      <c r="D91" s="20" t="inlineStr">
         <is>
           <t>Liquidation price</t>
         </is>
       </c>
-      <c r="E90" s="19">
-        <f>IF(B91=0,"",B90*(1-B92*(1/B91-B93/100)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+      <c r="E91" s="21">
+        <f>IF(B92=0,"",B91*(1-B93*(1/B92-B94/100)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
         <is>
           <t>Leverage</t>
         </is>
       </c>
-      <c r="B91" s="31" t="n">
+      <c r="B92" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="D91" s="18" t="inlineStr">
+      <c r="D92" s="20" t="inlineStr">
         <is>
           <t>Move to liquidation</t>
         </is>
       </c>
-      <c r="E91" s="21">
-        <f>IF(B90=0,"",E90/B90-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="16" t="inlineStr">
+      <c r="E92" s="23">
+        <f>IF(B91=0,"",E91/B91-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr">
         <is>
           <t>Side (1 long, -1 short)</t>
         </is>
       </c>
-      <c r="B92" s="24" t="n">
+      <c r="B93" s="27" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="16" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr">
         <is>
           <t>Maintenance margin</t>
         </is>
       </c>
-      <c r="B93" s="26" t="n">
+      <c r="B94" s="29" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="15" t="inlineStr">
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="17" t="inlineStr">
         <is>
           <t>Time-weighted return   ·   Lesson 8.5</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="16" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="18" t="inlineStr">
         <is>
           <t>Period 1 return</t>
         </is>
       </c>
-      <c r="B96" s="26" t="n">
+      <c r="B97" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="D96" s="18" t="inlineStr">
+      <c r="D97" s="20" t="inlineStr">
         <is>
           <t>Time-weighted return</t>
         </is>
       </c>
-      <c r="E96" s="28">
-        <f>(1+B96/100)*(1+B97/100)*(1+B98/100)*IF(B99="",1,1+B99/100)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="16" t="inlineStr">
+      <c r="E97" s="31">
+        <f>(1+B97/100)*(1+B98/100)*(1+B99/100)*IF(B100="",1,1+B100/100)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="inlineStr">
         <is>
           <t>Period 2 return</t>
         </is>
       </c>
-      <c r="B97" s="26" t="n">
+      <c r="B98" s="29" t="n">
         <v>-2</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="16" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="18" t="inlineStr">
         <is>
           <t>Period 3 return</t>
         </is>
       </c>
-      <c r="B98" s="26" t="n">
+      <c r="B99" s="29" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="16" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
         <is>
           <t>Period 4 return</t>
         </is>
       </c>
-      <c r="B99" s="26" t="n"/>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="15" t="inlineStr">
+      <c r="B100" s="29" t="n"/>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="17" t="inlineStr">
         <is>
           <t>CDP mint   ·   Lesson 3.7</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="16" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="18" t="inlineStr">
         <is>
           <t>Collateral quantity</t>
         </is>
       </c>
-      <c r="B102" s="17" t="n">
+      <c r="B103" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D102" s="18" t="inlineStr">
+      <c r="D103" s="20" t="inlineStr">
         <is>
           <t>Collateral value</t>
         </is>
       </c>
-      <c r="E102" s="19">
-        <f>B102*B103</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="16" t="inlineStr">
+      <c r="E103" s="21">
+        <f>B103*B104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr">
         <is>
           <t>Collateral price</t>
         </is>
       </c>
-      <c r="B103" s="20" t="n">
+      <c r="B104" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="D103" s="18" t="inlineStr">
+      <c r="D104" s="20" t="inlineStr">
         <is>
           <t>Maximum mint</t>
         </is>
       </c>
-      <c r="E103" s="19">
-        <f>IF(B105=0,"",E102/(B105/100))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="16" t="inlineStr">
+      <c r="E104" s="21">
+        <f>IF(B106=0,"",E103/(B106/100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
         <is>
           <t>Stablecoins to mint</t>
         </is>
       </c>
-      <c r="B104" s="20" t="n">
+      <c r="B105" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="D104" s="18" t="inlineStr">
+      <c r="D105" s="20" t="inlineStr">
         <is>
           <t>Collateral ratio</t>
         </is>
       </c>
-      <c r="E104" s="32">
-        <f>IF(B104=0,"",E102/B104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="16" t="inlineStr">
+      <c r="E105" s="34">
+        <f>IF(B105=0,"",E103/B105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
         <is>
           <t>Minimum collateral ratio</t>
         </is>
       </c>
-      <c r="B105" s="33" t="n">
+      <c r="B106" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="D105" s="18" t="inlineStr">
+      <c r="D106" s="20" t="inlineStr">
         <is>
           <t>Liquidation price</t>
         </is>
       </c>
-      <c r="E105" s="19">
-        <f>IF(B102=0,"",B104*(B105/100)/B102)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="16" t="inlineStr">
+      <c r="E106" s="21">
+        <f>IF(B103=0,"",B105*(B106/100)/B103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="inlineStr">
         <is>
           <t>Stability fee per year</t>
         </is>
       </c>
-      <c r="B106" s="26" t="n">
+      <c r="B107" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="D106" s="18" t="inlineStr">
+      <c r="D107" s="20" t="inlineStr">
         <is>
           <t>Stability fee per year</t>
         </is>
       </c>
-      <c r="E106" s="19">
-        <f>B104*B106/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="15" t="inlineStr">
+      <c r="E107" s="21">
+        <f>B105*B107/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="17" t="inlineStr">
         <is>
           <t>Funding carry   ·   Lesson 10.2</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="16" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
         <is>
           <t>Funding rate per 8 hours</t>
         </is>
       </c>
-      <c r="B109" s="26" t="n">
+      <c r="B110" s="29" t="n">
         <v>0.01</v>
       </c>
-      <c r="D109" s="18" t="inlineStr">
+      <c r="D110" s="20" t="inlineStr">
         <is>
           <t>APR on the hedged size</t>
         </is>
       </c>
-      <c r="E109" s="25">
-        <f>B109*3*365</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="16" t="inlineStr">
+      <c r="E110" s="28">
+        <f>B110*3*365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="18" t="inlineStr">
         <is>
           <t>Short leverage</t>
         </is>
       </c>
-      <c r="B110" s="31" t="n">
+      <c r="B111" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="D110" s="18" t="inlineStr">
+      <c r="D111" s="20" t="inlineStr">
         <is>
           <t>Return on total capital</t>
         </is>
       </c>
-      <c r="E110" s="25">
-        <f>IF(B110=0,"",E109/(1+1/B110))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="D111" s="18" t="inlineStr">
+      <c r="E111" s="28">
+        <f>IF(B111=0,"",E110/(1+1/B111))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="D112" s="20" t="inlineStr">
         <is>
           <t>Short liquidates near</t>
         </is>
       </c>
-      <c r="E111" s="32">
-        <f>IF(B110=0,"",1/B110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="1">
-      <c r="A113" s="15" t="inlineStr">
+      <c r="E112" s="34">
+        <f>IF(B111=0,"",1/B111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="17" t="inlineStr">
         <is>
           <t>One-day value at risk   ·   Lesson 8.7</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B114" s="20" t="n">
+      <c r="B115" s="22" t="n">
         <v>100000</v>
       </c>
-      <c r="D114" s="18" t="inlineStr">
+      <c r="D115" s="20" t="inlineStr">
         <is>
           <t>One-day VaR</t>
         </is>
       </c>
-      <c r="E114" s="19">
-        <f>B116*(B115/100)/SQRT(365)*B114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
+      <c r="E115" s="21">
+        <f>B117*(B116/100)/SQRT(365)*B115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
         <is>
           <t>Volatility per year</t>
         </is>
       </c>
-      <c r="B115" s="26" t="n">
+      <c r="B116" s="29" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="16" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
         <is>
           <t>Z score</t>
         </is>
       </c>
-      <c r="B116" s="17" t="n">
+      <c r="B117" s="19" t="n">
         <v>1.65</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="23">
-    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A74:E74"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B9 B15 B39 B40 B49 B70 B71 B77 B87 B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use 0 to 1" error="Enter a number from 0 to 1. 0.80 means 80%." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G5" location="'Tools'!A6" tooltip="Health factor and liquidation price"/>
+    <hyperlink ref="G6" location="'Tools'!A14" tooltip="Leveraged loop"/>
+    <hyperlink ref="G7" location="'Tools'!A20" tooltip="Impermanent loss vs holding"/>
+    <hyperlink ref="G8" location="'Tools'!A23" tooltip="LP fee breakeven"/>
+    <hyperlink ref="G9" location="'Tools'!A29" tooltip="Concentrated liquidity efficiency"/>
+    <hyperlink ref="G10" location="'Tools'!A33" tooltip="Loss versus rebalancing"/>
+    <hyperlink ref="G11" location="'Tools'!A37" tooltip="Lending supply APY"/>
+    <hyperlink ref="G12" location="'Tools'!A42" tooltip="APR, APY, and gas"/>
+    <hyperlink ref="G13" location="'Tools'!A48" tooltip="Airdrop expected value"/>
+    <hyperlink ref="G14" location="'Tools'!A53" tooltip="Principal token fixed yield"/>
+    <hyperlink ref="G15" location="'Tools'!A57" tooltip="Cash-and-carry basis"/>
+    <hyperlink ref="G16" location="'Tools'!A62" tooltip="Covered call"/>
+    <hyperlink ref="G17" location="'Tools'!A68" tooltip="Risk-adjusted yield"/>
+    <hyperlink ref="G18" location="'Tools'!A74" tooltip="Income and payout"/>
+    <hyperlink ref="G19" location="'Tools'!A80" tooltip="Balance sheet check"/>
+    <hyperlink ref="G20" location="'Tools'!A90" tooltip="Perp liquidation price"/>
+    <hyperlink ref="G21" location="'Tools'!A96" tooltip="Time-weighted return"/>
+    <hyperlink ref="G22" location="'Tools'!A102" tooltip="CDP mint"/>
+    <hyperlink ref="G23" location="'Tools'!A109" tooltip="Funding carry"/>
+    <hyperlink ref="G24" location="'Tools'!A114" tooltip="One-day value at risk"/>
+  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5116,7 +5498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5199,444 +5581,466 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="34" t="n"/>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="37" t="n"/>
-      <c r="F5" s="37" t="n"/>
-      <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
-      <c r="I5" s="35" t="n"/>
+      <c r="A5" s="36" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="38" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="37" t="n"/>
+      <c r="H5" s="37" t="n"/>
+      <c r="I5" s="37" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="34" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="37" t="n"/>
-      <c r="F6" s="37" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
-      <c r="I6" s="35" t="n"/>
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="37" t="n"/>
+      <c r="H6" s="37" t="n"/>
+      <c r="I6" s="37" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="34" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="37" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="35" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="37" t="n"/>
+      <c r="H7" s="37" t="n"/>
+      <c r="I7" s="37" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="34" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="37" t="n"/>
+      <c r="H8" s="37" t="n"/>
+      <c r="I8" s="37" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="34" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="35" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="37" t="n"/>
+      <c r="H9" s="37" t="n"/>
+      <c r="I9" s="37" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="34" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="37" t="n"/>
+      <c r="H10" s="37" t="n"/>
+      <c r="I10" s="37" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="34" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="37" t="n"/>
+      <c r="I11" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="34" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="37" t="n"/>
+      <c r="H12" s="37" t="n"/>
+      <c r="I12" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="34" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="34" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="37" t="n"/>
+      <c r="H14" s="37" t="n"/>
+      <c r="I14" s="37" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="34" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="37" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="37" t="n"/>
+      <c r="H15" s="37" t="n"/>
+      <c r="I15" s="37" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="34" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="37" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="38" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="37" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="37" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="34" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="37" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="38" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="37" t="n"/>
+      <c r="H17" s="37" t="n"/>
+      <c r="I17" s="37" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="34" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="37" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="37" t="n"/>
+      <c r="H18" s="37" t="n"/>
+      <c r="I18" s="37" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="34" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="37" t="n"/>
-      <c r="F19" s="37" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="37" t="n"/>
+      <c r="H19" s="37" t="n"/>
+      <c r="I19" s="37" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="34" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="37" t="n"/>
-      <c r="F20" s="37" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="37" t="n"/>
+      <c r="H20" s="37" t="n"/>
+      <c r="I20" s="37" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="34" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="37" t="n"/>
-      <c r="F21" s="37" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="37" t="n"/>
+      <c r="H21" s="37" t="n"/>
+      <c r="I21" s="37" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="34" t="n"/>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="37" t="n"/>
-      <c r="F22" s="37" t="n"/>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="35" t="n"/>
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="38" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="37" t="n"/>
+      <c r="I22" s="37" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="34" t="n"/>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="37" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
+      <c r="A23" s="36" t="n"/>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="38" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="37" t="n"/>
+      <c r="H23" s="37" t="n"/>
+      <c r="I23" s="37" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="34" t="n"/>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="37" t="n"/>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="37" t="n"/>
+      <c r="H24" s="37" t="n"/>
+      <c r="I24" s="37" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="34" t="n"/>
-      <c r="B25" s="35" t="n"/>
-      <c r="C25" s="35" t="n"/>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="37" t="n"/>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
+      <c r="A25" s="36" t="n"/>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="37" t="n"/>
+      <c r="H25" s="37" t="n"/>
+      <c r="I25" s="37" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="34" t="n"/>
-      <c r="B26" s="35" t="n"/>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="37" t="n"/>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
+      <c r="A26" s="36" t="n"/>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="37" t="n"/>
+      <c r="H26" s="37" t="n"/>
+      <c r="I26" s="37" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="34" t="n"/>
-      <c r="B27" s="35" t="n"/>
-      <c r="C27" s="35" t="n"/>
-      <c r="D27" s="36" t="n"/>
-      <c r="E27" s="37" t="n"/>
-      <c r="F27" s="37" t="n"/>
-      <c r="G27" s="35" t="n"/>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="35" t="n"/>
+      <c r="A27" s="36" t="n"/>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="37" t="n"/>
+      <c r="H27" s="37" t="n"/>
+      <c r="I27" s="37" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="34" t="n"/>
-      <c r="B28" s="35" t="n"/>
-      <c r="C28" s="35" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
-      <c r="G28" s="35" t="n"/>
-      <c r="H28" s="35" t="n"/>
-      <c r="I28" s="35" t="n"/>
+      <c r="A28" s="36" t="n"/>
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="37" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="37" t="n"/>
+      <c r="H28" s="37" t="n"/>
+      <c r="I28" s="37" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="34" t="n"/>
-      <c r="B29" s="35" t="n"/>
-      <c r="C29" s="35" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="37" t="n"/>
-      <c r="F29" s="37" t="n"/>
-      <c r="G29" s="35" t="n"/>
-      <c r="H29" s="35" t="n"/>
-      <c r="I29" s="35" t="n"/>
+      <c r="A29" s="36" t="n"/>
+      <c r="B29" s="37" t="n"/>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="37" t="n"/>
+      <c r="H29" s="37" t="n"/>
+      <c r="I29" s="37" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="34" t="n"/>
-      <c r="B30" s="35" t="n"/>
-      <c r="C30" s="35" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="37" t="n"/>
-      <c r="F30" s="37" t="n"/>
-      <c r="G30" s="35" t="n"/>
-      <c r="H30" s="35" t="n"/>
-      <c r="I30" s="35" t="n"/>
+      <c r="A30" s="36" t="n"/>
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="38" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="37" t="n"/>
+      <c r="H30" s="37" t="n"/>
+      <c r="I30" s="37" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="34" t="n"/>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="37" t="n"/>
-      <c r="F31" s="37" t="n"/>
-      <c r="G31" s="35" t="n"/>
-      <c r="H31" s="35" t="n"/>
-      <c r="I31" s="35" t="n"/>
+      <c r="A31" s="36" t="n"/>
+      <c r="B31" s="37" t="n"/>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="38" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="37" t="n"/>
+      <c r="H31" s="37" t="n"/>
+      <c r="I31" s="37" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="34" t="n"/>
-      <c r="B32" s="35" t="n"/>
-      <c r="C32" s="35" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="37" t="n"/>
-      <c r="F32" s="37" t="n"/>
-      <c r="G32" s="35" t="n"/>
-      <c r="H32" s="35" t="n"/>
-      <c r="I32" s="35" t="n"/>
+      <c r="A32" s="36" t="n"/>
+      <c r="B32" s="37" t="n"/>
+      <c r="C32" s="37" t="n"/>
+      <c r="D32" s="38" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="37" t="n"/>
+      <c r="H32" s="37" t="n"/>
+      <c r="I32" s="37" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="34" t="n"/>
-      <c r="B33" s="35" t="n"/>
-      <c r="C33" s="35" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="37" t="n"/>
-      <c r="F33" s="37" t="n"/>
-      <c r="G33" s="35" t="n"/>
-      <c r="H33" s="35" t="n"/>
-      <c r="I33" s="35" t="n"/>
+      <c r="A33" s="36" t="n"/>
+      <c r="B33" s="37" t="n"/>
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="37" t="n"/>
+      <c r="H33" s="37" t="n"/>
+      <c r="I33" s="37" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="34" t="n"/>
-      <c r="B34" s="35" t="n"/>
-      <c r="C34" s="35" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="37" t="n"/>
-      <c r="G34" s="35" t="n"/>
-      <c r="H34" s="35" t="n"/>
-      <c r="I34" s="35" t="n"/>
+      <c r="A34" s="36" t="n"/>
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="37" t="n"/>
+      <c r="H34" s="37" t="n"/>
+      <c r="I34" s="37" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="34" t="n"/>
-      <c r="B35" s="35" t="n"/>
-      <c r="C35" s="35" t="n"/>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="37" t="n"/>
-      <c r="G35" s="35" t="n"/>
-      <c r="H35" s="35" t="n"/>
-      <c r="I35" s="35" t="n"/>
+      <c r="A35" s="36" t="n"/>
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="38" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="37" t="n"/>
+      <c r="H35" s="37" t="n"/>
+      <c r="I35" s="37" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="34" t="n"/>
-      <c r="B36" s="35" t="n"/>
-      <c r="C36" s="35" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="37" t="n"/>
-      <c r="F36" s="37" t="n"/>
-      <c r="G36" s="35" t="n"/>
-      <c r="H36" s="35" t="n"/>
-      <c r="I36" s="35" t="n"/>
+      <c r="A36" s="36" t="n"/>
+      <c r="B36" s="37" t="n"/>
+      <c r="C36" s="37" t="n"/>
+      <c r="D36" s="38" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="37" t="n"/>
+      <c r="H36" s="37" t="n"/>
+      <c r="I36" s="37" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="34" t="n"/>
-      <c r="B37" s="35" t="n"/>
-      <c r="C37" s="35" t="n"/>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="37" t="n"/>
-      <c r="F37" s="37" t="n"/>
-      <c r="G37" s="35" t="n"/>
-      <c r="H37" s="35" t="n"/>
-      <c r="I37" s="35" t="n"/>
+      <c r="A37" s="36" t="n"/>
+      <c r="B37" s="37" t="n"/>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="37" t="n"/>
+      <c r="H37" s="37" t="n"/>
+      <c r="I37" s="37" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="34" t="n"/>
-      <c r="B38" s="35" t="n"/>
-      <c r="C38" s="35" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="37" t="n"/>
-      <c r="F38" s="37" t="n"/>
-      <c r="G38" s="35" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
+      <c r="A38" s="36" t="n"/>
+      <c r="B38" s="37" t="n"/>
+      <c r="C38" s="37" t="n"/>
+      <c r="D38" s="38" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="37" t="n"/>
+      <c r="H38" s="37" t="n"/>
+      <c r="I38" s="37" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="34" t="n"/>
-      <c r="B39" s="35" t="n"/>
-      <c r="C39" s="35" t="n"/>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="37" t="n"/>
-      <c r="F39" s="37" t="n"/>
-      <c r="G39" s="35" t="n"/>
-      <c r="H39" s="35" t="n"/>
-      <c r="I39" s="35" t="n"/>
+      <c r="A39" s="36" t="n"/>
+      <c r="B39" s="37" t="n"/>
+      <c r="C39" s="37" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="37" t="n"/>
+      <c r="H39" s="37" t="n"/>
+      <c r="I39" s="37" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="34" t="n"/>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="36" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-      <c r="G40" s="35" t="n"/>
-      <c r="H40" s="35" t="n"/>
-      <c r="I40" s="35" t="n"/>
+      <c r="A40" s="36" t="n"/>
+      <c r="B40" s="37" t="n"/>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="38" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="37" t="n"/>
+      <c r="H40" s="37" t="n"/>
+      <c r="I40" s="37" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="34" t="n"/>
-      <c r="B41" s="35" t="n"/>
-      <c r="C41" s="35" t="n"/>
-      <c r="D41" s="36" t="n"/>
-      <c r="E41" s="37" t="n"/>
-      <c r="F41" s="37" t="n"/>
-      <c r="G41" s="35" t="n"/>
-      <c r="H41" s="35" t="n"/>
-      <c r="I41" s="35" t="n"/>
+      <c r="A41" s="36" t="n"/>
+      <c r="B41" s="37" t="n"/>
+      <c r="C41" s="37" t="n"/>
+      <c r="D41" s="38" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="37" t="n"/>
+      <c r="H41" s="37" t="n"/>
+      <c r="I41" s="37" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="34" t="n"/>
-      <c r="B42" s="35" t="n"/>
-      <c r="C42" s="35" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="37" t="n"/>
-      <c r="F42" s="37" t="n"/>
-      <c r="G42" s="35" t="n"/>
-      <c r="H42" s="35" t="n"/>
-      <c r="I42" s="35" t="n"/>
+      <c r="A42" s="36" t="n"/>
+      <c r="B42" s="37" t="n"/>
+      <c r="C42" s="37" t="n"/>
+      <c r="D42" s="38" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="37" t="n"/>
+      <c r="H42" s="37" t="n"/>
+      <c r="I42" s="37" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="34" t="n"/>
-      <c r="B43" s="35" t="n"/>
-      <c r="C43" s="35" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="37" t="n"/>
-      <c r="F43" s="37" t="n"/>
-      <c r="G43" s="35" t="n"/>
-      <c r="H43" s="35" t="n"/>
-      <c r="I43" s="35" t="n"/>
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="37" t="n"/>
+      <c r="C43" s="37" t="n"/>
+      <c r="D43" s="38" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="37" t="n"/>
+      <c r="H43" s="37" t="n"/>
+      <c r="I43" s="37" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="34" t="n"/>
-      <c r="B44" s="35" t="n"/>
-      <c r="C44" s="35" t="n"/>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="37" t="n"/>
-      <c r="F44" s="37" t="n"/>
-      <c r="G44" s="35" t="n"/>
-      <c r="H44" s="35" t="n"/>
-      <c r="I44" s="35" t="n"/>
+      <c r="A44" s="36" t="n"/>
+      <c r="B44" s="37" t="n"/>
+      <c r="C44" s="37" t="n"/>
+      <c r="D44" s="38" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="37" t="n"/>
+      <c r="H44" s="37" t="n"/>
+      <c r="I44" s="37" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>Lines with a date</t>
+        </is>
+      </c>
+      <c r="B46" s="40">
+        <f>COUNTA(A5:A44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Fees recorded</t>
+        </is>
+      </c>
+      <c r="B47" s="21">
+        <f>SUM(F5:F44)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -5760,244 +6164,244 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="n"/>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
-      <c r="I5" s="35" t="n"/>
-      <c r="J5" s="35" t="n"/>
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="37" t="n"/>
+      <c r="H5" s="37" t="n"/>
+      <c r="I5" s="37" t="n"/>
+      <c r="J5" s="37" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
-      <c r="I6" s="35" t="n"/>
-      <c r="J6" s="35" t="n"/>
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="37" t="n"/>
+      <c r="H6" s="37" t="n"/>
+      <c r="I6" s="37" t="n"/>
+      <c r="J6" s="37" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="35" t="n"/>
-      <c r="J7" s="35" t="n"/>
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="37" t="n"/>
+      <c r="H7" s="37" t="n"/>
+      <c r="I7" s="37" t="n"/>
+      <c r="J7" s="37" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
-      <c r="J8" s="35" t="n"/>
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="37" t="n"/>
+      <c r="H8" s="37" t="n"/>
+      <c r="I8" s="37" t="n"/>
+      <c r="J8" s="37" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="35" t="n"/>
-      <c r="J9" s="35" t="n"/>
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="37" t="n"/>
+      <c r="G9" s="37" t="n"/>
+      <c r="H9" s="37" t="n"/>
+      <c r="I9" s="37" t="n"/>
+      <c r="J9" s="37" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="35" t="n"/>
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="37" t="n"/>
+      <c r="H10" s="37" t="n"/>
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="37" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
-      <c r="J11" s="35" t="n"/>
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="37" t="n"/>
+      <c r="I11" s="37" t="n"/>
+      <c r="J11" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
-      <c r="J12" s="35" t="n"/>
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="37" t="n"/>
+      <c r="H12" s="37" t="n"/>
+      <c r="I12" s="37" t="n"/>
+      <c r="J12" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
-      <c r="J13" s="35" t="n"/>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="37" t="n"/>
+      <c r="H14" s="37" t="n"/>
+      <c r="I14" s="37" t="n"/>
+      <c r="J14" s="37" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
-      <c r="J15" s="35" t="n"/>
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="37" t="n"/>
+      <c r="H15" s="37" t="n"/>
+      <c r="I15" s="37" t="n"/>
+      <c r="J15" s="37" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
-      <c r="J16" s="35" t="n"/>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="37" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="37" t="n"/>
+      <c r="J16" s="37" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="35" t="n"/>
-      <c r="J17" s="35" t="n"/>
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="37" t="n"/>
+      <c r="H17" s="37" t="n"/>
+      <c r="I17" s="37" t="n"/>
+      <c r="J17" s="37" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="n"/>
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="37" t="n"/>
+      <c r="H18" s="37" t="n"/>
+      <c r="I18" s="37" t="n"/>
+      <c r="J18" s="37" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="35" t="n"/>
-      <c r="J19" s="35" t="n"/>
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="37" t="n"/>
+      <c r="H19" s="37" t="n"/>
+      <c r="I19" s="37" t="n"/>
+      <c r="J19" s="37" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
-      <c r="J20" s="35" t="n"/>
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="37" t="n"/>
+      <c r="H20" s="37" t="n"/>
+      <c r="I20" s="37" t="n"/>
+      <c r="J20" s="37" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
-      <c r="J21" s="35" t="n"/>
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="37" t="n"/>
+      <c r="H21" s="37" t="n"/>
+      <c r="I21" s="37" t="n"/>
+      <c r="J21" s="37" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="35" t="n"/>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="35" t="n"/>
-      <c r="J22" s="35" t="n"/>
+      <c r="A22" s="37" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="37" t="n"/>
+      <c r="I22" s="37" t="n"/>
+      <c r="J22" s="37" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="35" t="n"/>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
-      <c r="J23" s="35" t="n"/>
+      <c r="A23" s="37" t="n"/>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="37" t="n"/>
+      <c r="H23" s="37" t="n"/>
+      <c r="I23" s="37" t="n"/>
+      <c r="J23" s="37" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="35" t="n"/>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="35" t="n"/>
+      <c r="A24" s="37" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="37" t="n"/>
+      <c r="H24" s="37" t="n"/>
+      <c r="I24" s="37" t="n"/>
+      <c r="J24" s="37" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -6056,196 +6460,196 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Protocol</t>
         </is>
       </c>
-      <c r="B5" s="38" t="n"/>
+      <c r="B5" s="41" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n"/>
+      <c r="B6" s="41" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>TVL</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n"/>
+      <c r="B7" s="41" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>TVL source and date</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n"/>
+      <c r="B8" s="41" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Risk rating (low, medium, high)</t>
         </is>
       </c>
-      <c r="B9" s="38" t="n"/>
+      <c r="B9" s="41" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Verdict (use, watch, pass)</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
+      <c r="B10" s="41" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>1 Mechanism</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n"/>
+      <c r="B12" s="41" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2 Cash flow (organic vs subsidised)</t>
         </is>
       </c>
-      <c r="B13" s="38" t="n"/>
+      <c r="B13" s="41" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>3 Dependencies</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n"/>
+      <c r="B14" s="41" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>4 Solvency</t>
         </is>
       </c>
-      <c r="B15" s="38" t="n"/>
+      <c r="B15" s="41" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>5 Evidence (links)</t>
         </is>
       </c>
-      <c r="B16" s="38" t="n"/>
+      <c r="B16" s="41" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>6 Exit</t>
         </is>
       </c>
-      <c r="B17" s="38" t="n"/>
+      <c r="B17" s="41" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Market cap</t>
         </is>
       </c>
-      <c r="B19" s="38" t="n"/>
+      <c r="B19" s="41" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Fully diluted value</t>
         </is>
       </c>
-      <c r="B20" s="38" t="n"/>
+      <c r="B20" s="41" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Unlocks in the next 12 months</t>
         </is>
       </c>
-      <c r="B21" s="38" t="n"/>
+      <c r="B21" s="41" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Value capture</t>
         </is>
       </c>
-      <c r="B22" s="38" t="n"/>
+      <c r="B22" s="41" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Voting concentration</t>
         </is>
       </c>
-      <c r="B24" s="38" t="n"/>
+      <c r="B24" s="41" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Timelock</t>
         </is>
       </c>
-      <c r="B25" s="38" t="n"/>
+      <c r="B25" s="41" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Holders</t>
         </is>
       </c>
-      <c r="B27" s="38" t="n"/>
+      <c r="B27" s="41" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Flows</t>
         </is>
       </c>
-      <c r="B28" s="38" t="n"/>
+      <c r="B28" s="41" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B29" s="38" t="n"/>
+      <c r="B29" s="41" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
       </c>
-      <c r="B30" s="38" t="n"/>
+      <c r="B30" s="41" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Derivatives</t>
         </is>
       </c>
-      <c r="B31" s="38" t="n"/>
+      <c r="B31" s="41" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Monitoring triggers</t>
         </is>
       </c>
-      <c r="B33" s="38" t="n"/>
+      <c r="B33" s="41" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -6353,332 +6757,332 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Example: looped ETH</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>economic</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Borrow rate rises above the collateral yield. Replace this row.</t>
         </is>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="40">
         <f>IF(OR(D5="",E5=""),"",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>Do not hold it until the response is real.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Example: stablecoin pool</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>smart-contract</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>A bug drains the pool. Replace this row.</t>
         </is>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="40">
         <f>IF(OR(D6="",E6=""),"",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>Write the mitigation before you size it.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="39">
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="40">
         <f>IF(OR(D7="",E7=""),"",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="35" t="n"/>
+      <c r="G7" s="37" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="39">
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="40">
         <f>IF(OR(D8="",E8=""),"",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="35" t="n"/>
+      <c r="G8" s="37" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="39">
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="40">
         <f>IF(OR(D9="",E9=""),"",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="35" t="n"/>
+      <c r="G9" s="37" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="39">
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="40">
         <f>IF(OR(D10="",E10=""),"",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="35" t="n"/>
+      <c r="G10" s="37" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="39">
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="40">
         <f>IF(OR(D11="",E11=""),"",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="35" t="n"/>
+      <c r="G11" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="39">
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="40">
         <f>IF(OR(D12="",E12=""),"",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="35" t="n"/>
+      <c r="G12" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="39">
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="40">
         <f>IF(OR(D13="",E13=""),"",D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="35" t="n"/>
+      <c r="G13" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="39">
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="40">
         <f>IF(OR(D14="",E14=""),"",D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="35" t="n"/>
+      <c r="G14" s="37" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="39">
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="40">
         <f>IF(OR(D15="",E15=""),"",D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="35" t="n"/>
+      <c r="G15" s="37" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="39">
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="40">
         <f>IF(OR(D16="",E16=""),"",D16*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="35" t="n"/>
+      <c r="G16" s="37" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="39">
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="40">
         <f>IF(OR(D17="",E17=""),"",D17*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="35" t="n"/>
+      <c r="G17" s="37" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="39">
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="40">
         <f>IF(OR(D18="",E18=""),"",D18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="35" t="n"/>
+      <c r="G18" s="37" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="39">
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="40">
         <f>IF(OR(D19="",E19=""),"",D19*E19)</f>
         <v/>
       </c>
-      <c r="G19" s="35" t="n"/>
+      <c r="G19" s="37" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="39">
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="40">
         <f>IF(OR(D20="",E20=""),"",D20*E20)</f>
         <v/>
       </c>
-      <c r="G20" s="35" t="n"/>
+      <c r="G20" s="37" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="39">
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="40">
         <f>IF(OR(D21="",E21=""),"",D21*E21)</f>
         <v/>
       </c>
-      <c r="G21" s="35" t="n"/>
+      <c r="G21" s="37" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="35" t="n"/>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="39">
+      <c r="A22" s="37" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="40">
         <f>IF(OR(D22="",E22=""),"",D22*E22)</f>
         <v/>
       </c>
-      <c r="G22" s="35" t="n"/>
+      <c r="G22" s="37" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="35" t="n"/>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="39">
+      <c r="A23" s="37" t="n"/>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="40">
         <f>IF(OR(D23="",E23=""),"",D23*E23)</f>
         <v/>
       </c>
-      <c r="G23" s="35" t="n"/>
+      <c r="G23" s="37" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="35" t="n"/>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="39">
+      <c r="A24" s="37" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="40">
         <f>IF(OR(D24="",E24=""),"",D24*E24)</f>
         <v/>
       </c>
-      <c r="G24" s="35" t="n"/>
+      <c r="G24" s="37" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="35" t="n"/>
-      <c r="B25" s="35" t="n"/>
-      <c r="C25" s="35" t="n"/>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="39">
+      <c r="A25" s="37" t="n"/>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="40">
         <f>IF(OR(D25="",E25=""),"",D25*E25)</f>
         <v/>
       </c>
-      <c r="G25" s="35" t="n"/>
+      <c r="G25" s="37" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="35" t="n"/>
-      <c r="B26" s="35" t="n"/>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="39">
+      <c r="A26" s="37" t="n"/>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="40">
         <f>IF(OR(D26="",E26=""),"",D26*E26)</f>
         <v/>
       </c>
-      <c r="G26" s="35" t="n"/>
+      <c r="G26" s="37" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="35" t="n"/>
-      <c r="B27" s="35" t="n"/>
-      <c r="C27" s="35" t="n"/>
-      <c r="D27" s="35" t="n"/>
-      <c r="E27" s="35" t="n"/>
-      <c r="F27" s="39">
+      <c r="A27" s="37" t="n"/>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="40">
         <f>IF(OR(D27="",E27=""),"",D27*E27)</f>
         <v/>
       </c>
-      <c r="G27" s="35" t="n"/>
+      <c r="G27" s="37" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="35" t="n"/>
-      <c r="B28" s="35" t="n"/>
-      <c r="C28" s="35" t="n"/>
-      <c r="D28" s="35" t="n"/>
-      <c r="E28" s="35" t="n"/>
-      <c r="F28" s="39">
+      <c r="A28" s="37" t="n"/>
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="37" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="40">
         <f>IF(OR(D28="",E28=""),"",D28*E28)</f>
         <v/>
       </c>
-      <c r="G28" s="35" t="n"/>
+      <c r="G28" s="37" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -6785,132 +7189,132 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="n"/>
-      <c r="B5" s="40" t="n"/>
-      <c r="C5" s="40" t="n"/>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="42" t="n"/>
+      <c r="C5" s="42" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="40" t="n"/>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="42" t="n"/>
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="40" t="n"/>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="42" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="40" t="n"/>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="42" t="n"/>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="40" t="n"/>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="37" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="40" t="n"/>
-      <c r="C10" s="40" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="40" t="n"/>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="42" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="40" t="n"/>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="40" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="40" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="40" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="40" t="n"/>
-      <c r="C16" s="40" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Target total</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="43">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Current total</t>
         </is>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="43">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Target check</t>
         </is>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="25">
         <f>IF(COUNT(B5:B16)=0,"",IF(ABS(B18-100)&lt;0.1,"Adds to 100%","Does not add to 100%"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Rebalance rule</t>
         </is>
       </c>
-      <c r="B22" s="38" t="n"/>
-      <c r="C22" s="42" t="n"/>
-      <c r="D22" s="42" t="n"/>
-      <c r="E22" s="43" t="n"/>
+      <c r="B22" s="41" t="n"/>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="45" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -6941,10 +7345,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -6965,190 +7369,198 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>The numbers already here are the lesson example: $300,000 collateral, $60,000 debt, $40,000 reserve. Replace them with yours. Educational only. Not financial, tax, or legal advice. Never type a seed phrase, private key, API key, or password.</t>
+          <t>The numbers already here are the lesson example: $300,000 collateral, $60,000 debt, $40,000 reserve. LTV, the health factor, and interest use loans plus margin. Yield positions sit in equity only. Educational only. Not financial, tax, or legal advice. Never type a seed phrase, private key, API key, or password.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Collateral</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="22" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Yield positions</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Reserve (cash you can reach)</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="22" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Other assets</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Loans</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="22" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Margin</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Other liabilities</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Liquidation threshold (0 to 1)</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="19" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Borrow APY</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="29" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Monthly spending</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="22" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="21">
         <f>B5+B6+B7+B8</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="21">
         <f>B10+B11+B12</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="21">
         <f>B18-B19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>LTV (loans ÷ collateral)</t>
-        </is>
-      </c>
-      <c r="B21" s="21">
-        <f>IF(B5=0,"",B10/B5)</f>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>LTV (loans + margin ÷ collateral)</t>
+        </is>
+      </c>
+      <c r="B21" s="23">
+        <f>IF(B5=0,"",(B10+B11)/B5)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Health factor on collateral</t>
         </is>
       </c>
-      <c r="B22" s="22">
-        <f>IF(OR(B10=0,B14=""),"",B5*B14/B10)</f>
+      <c r="B22" s="24">
+        <f>IF(OR((B10+B11)=0,B14=""),"",B5*B14/(B10+B11))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>Monthly interest</t>
-        </is>
-      </c>
-      <c r="B23" s="19">
-        <f>IF(B15="","",B10*B15/100/12)</f>
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Monthly interest on loans and margin</t>
+        </is>
+      </c>
+      <c r="B23" s="21">
+        <f>IF(B15="","",(B10+B11)*B15/100/12)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Reserve runway (months)</t>
         </is>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="32">
         <f>IF((B16+B23)=0,"",B7/(B16+B23))</f>
         <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>Yield positions are inside equity. They are not treated as collateral on this sheet.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
@@ -7158,6 +7570,12 @@
       <formula>AND(ISNUMBER(B22),B22&lt;1.5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use 0 to 1" error="Enter a number from 0 to 1. 0.80 means 80%." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -7209,76 +7627,76 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Vault type (for example 2 of 3 multisig)</t>
         </is>
       </c>
-      <c r="B5" s="38" t="n"/>
+      <c r="B5" s="41" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Key holders, by role</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n"/>
+      <c r="B6" s="41" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Allowlisted destinations, described generally</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n"/>
+      <c r="B7" s="41" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Timelock</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n"/>
+      <c r="B8" s="41" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Operating wallet type</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
+      <c r="B10" s="41" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Daily limit</t>
         </is>
       </c>
-      <c r="B11" s="38" t="n"/>
+      <c r="B11" s="41" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Protocols the operating wallet may use</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n"/>
+      <c r="B12" s="41" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Hot float size</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n"/>
+      <c r="B14" s="41" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Refill schedule</t>
         </is>
       </c>
-      <c r="B15" s="38" t="n"/>
+      <c r="B15" s="41" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -7298,44 +7716,44 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="35" t="n"/>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
+      <c r="A22" s="37" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="35" t="n"/>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
+      <c r="A23" s="37" t="n"/>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="35" t="n"/>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
+      <c r="A24" s="37" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="35" t="n"/>
-      <c r="B25" s="35" t="n"/>
-      <c r="C25" s="35" t="n"/>
+      <c r="A25" s="37" t="n"/>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
